--- a/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/PseudoAnnotated/Pseudo_annotated_prev.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/PseudoAnnotated/Pseudo_annotated_prev.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AtsisiuntimasZiveDuomenu\PseudoAnnotated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948F0353-63E8-4BC5-A8EE-D0BE97129319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451928F7-CF2A-4B78-80E6-4435ECE3EB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Records" sheetId="1" r:id="rId1"/>
-    <sheet name="Marks" sheetId="4" r:id="rId2"/>
+    <sheet name="Marks" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="256">
   <si>
     <t>filename</t>
   </si>
@@ -122,27 +122,30 @@
     <t>Amplitudės (mV) svyravimai</t>
   </si>
   <si>
+    <t>excl</t>
+  </si>
+  <si>
+    <t>PSEUDO_ANNOTATED</t>
+  </si>
+  <si>
+    <t>615516b62312e50c3f168e38</t>
+  </si>
+  <si>
+    <t>6034c808d6c2740008035ede</t>
+  </si>
+  <si>
+    <t>Labai ilgas, &gt; 4000. Praleistas pikas, gydytojas pažymėjo. Kokybė nėra aiški</t>
+  </si>
+  <si>
+    <t>1001_1</t>
+  </si>
+  <si>
+    <t>1626330.744</t>
+  </si>
+  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>PSEUDO_ANNOTATED</t>
-  </si>
-  <si>
-    <t>615516b62312e50c3f168e38</t>
-  </si>
-  <si>
-    <t>6034c808d6c2740008035ede</t>
-  </si>
-  <si>
-    <t>Labai ilgas, &gt; 4000. Praleistas pikas, gydytojas pažymėjo. Kokybė nėra aiški</t>
-  </si>
-  <si>
-    <t>1001_1</t>
-  </si>
-  <si>
-    <t>1626330.744</t>
-  </si>
-  <si>
     <t>Yra S</t>
   </si>
   <si>
@@ -161,9 +164,6 @@
     <t>1626934.963</t>
   </si>
   <si>
-    <t>xx</t>
-  </si>
-  <si>
     <t>60f9188487cf6632713780c5</t>
   </si>
   <si>
@@ -206,9 +206,6 @@
     <t>1630762.273</t>
   </si>
   <si>
-    <t>testavimui</t>
-  </si>
-  <si>
     <t>613f58593d08d401b0cdccf4</t>
   </si>
   <si>
@@ -293,6 +290,9 @@
     <t>Ž:  Kelis kartus po skilvelinės ekstrasistolės šiame įraše stebime vadinamus "fusion beat" (susiliejęs kompleksas). Jį lemia tai, jog skilvelių depoliarizaciją lemia tiek neseniai buvusi skilvelinė ekstrasistolė, tiek iš sinusinio mazgo atėjęs impulsas ir šios dvi skilvelio aktyvacijos susilieja, todėl keičia morfologiją, palyginus su įprastu sinusiniu kompleksu, tačiau nėra platus kaip skilvelinė ekstrasistolė. Šiuo atveju tai nėra nei skilvelinė, nei prieširdinė ekstrasistolės, nei normalus QRS kompleksas. Tam, kad neklaidinti algoritmo pažymėjau juos U raide.</t>
   </si>
   <si>
+    <t>ect8,nz8</t>
+  </si>
+  <si>
     <t>FULLY_ANNOTATED_PROFESSIONALLY; FOR_EXTERNAL_ANNOTATING</t>
   </si>
   <si>
@@ -767,28 +767,28 @@
     <t>mark stulpelyje žymima kokiems sarašams priskiriamas įrašas</t>
   </si>
   <si>
-    <t>sąrašas ektopinių pūpsnių anotavimui ir triukšmų žymėjimui</t>
+    <t>eliminuojamas įrašas iš mokymo ir testinės imčių</t>
   </si>
   <si>
     <t>ect8</t>
   </si>
   <si>
+    <t>nz8</t>
+  </si>
+  <si>
     <t>sąrašas  triukšmų žymėjimui</t>
   </si>
   <si>
-    <t>nz8</t>
-  </si>
-  <si>
-    <t>ect8,nz8</t>
-  </si>
-  <si>
     <t>abu sąrašai</t>
   </si>
   <si>
-    <t>eliminuojamas įrašas iš mokymo ir testinės imčių</t>
-  </si>
-  <si>
-    <t>excl</t>
+    <t>sąrašas ektopinių pūpsnių anotavimui</t>
+  </si>
+  <si>
+    <t>ect9,nz9</t>
+  </si>
+  <si>
+    <t>ect9</t>
   </si>
 </sst>
 </file>
@@ -894,7 +894,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -922,13 +922,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1217,11 +1216,11 @@
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.36328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.1796875" customWidth="1"/>
-    <col min="7" max="7" width="24.26953125" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
     <col min="8" max="8" width="9.90625" style="13" customWidth="1"/>
     <col min="9" max="9" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.81640625" bestFit="1" customWidth="1"/>
@@ -1232,15 +1231,15 @@
     <col min="15" max="15" width="4.08984375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="4.1796875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.36328125" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="8.36328125" customWidth="1"/>
     <col min="19" max="19" width="10.08984375" customWidth="1"/>
     <col min="20" max="20" width="5.08984375" customWidth="1"/>
     <col min="21" max="21" width="5.453125" customWidth="1"/>
     <col min="22" max="22" width="5.1796875" customWidth="1"/>
     <col min="23" max="23" width="6.453125" customWidth="1"/>
-    <col min="24" max="24" width="9.453125" hidden="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.36328125" hidden="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.453125" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.453125" customWidth="1"/>
+    <col min="25" max="25" width="9.36328125" customWidth="1"/>
+    <col min="26" max="26" width="11.453125" customWidth="1"/>
     <col min="27" max="27" width="19.36328125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="25.36328125" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="25" bestFit="1" customWidth="1"/>
@@ -1367,7 +1366,7 @@
         <v>32</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>255</v>
+        <v>33</v>
       </c>
       <c r="I2" s="5">
         <v>4850</v>
@@ -1457,14 +1456,14 @@
       <c r="E3">
         <v>5</v>
       </c>
-      <c r="F3" t="s">
-        <v>33</v>
+      <c r="F3">
+        <v>2222</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>33</v>
+        <v>254</v>
       </c>
       <c r="I3" s="5">
         <v>797</v>
@@ -1524,13 +1523,13 @@
         <v>34</v>
       </c>
       <c r="AB3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AC3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
@@ -1540,13 +1539,13 @@
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4">
         <v>115199</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1554,11 +1553,11 @@
       <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" t="s">
-        <v>33</v>
+      <c r="F4">
+        <v>1111</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>46</v>
+        <v>254</v>
       </c>
       <c r="I4" s="5">
         <v>763</v>
@@ -1621,7 +1620,7 @@
         <v>47</v>
       </c>
       <c r="AC4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AD4" s="11" t="s">
         <v>48</v>
@@ -1648,11 +1647,11 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" t="s">
-        <v>33</v>
+      <c r="F5">
+        <v>1111</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>33</v>
+        <v>254</v>
       </c>
       <c r="I5" s="5">
         <v>654</v>
@@ -1742,11 +1741,11 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" t="s">
-        <v>33</v>
+      <c r="F6">
+        <v>1111</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>33</v>
+        <v>254</v>
       </c>
       <c r="I6" s="5">
         <v>840</v>
@@ -1836,14 +1835,11 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" t="s">
-        <v>61</v>
+      <c r="F7">
+        <v>2222</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>33</v>
+        <v>255</v>
       </c>
       <c r="I7" s="5">
         <v>886</v>
@@ -1903,13 +1899,13 @@
         <v>34</v>
       </c>
       <c r="AB7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AC7" t="s">
         <v>57</v>
       </c>
       <c r="AD7" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AE7" s="11"/>
       <c r="AF7" s="11"/>
@@ -1919,13 +1915,13 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B8">
         <v>127999</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1933,11 +1929,11 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" t="s">
-        <v>33</v>
+      <c r="F8">
+        <v>3333</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>33</v>
+        <v>255</v>
       </c>
       <c r="I8" s="5">
         <v>974</v>
@@ -1997,7 +1993,7 @@
         <v>34</v>
       </c>
       <c r="AB8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AC8" t="s">
         <v>57</v>
@@ -2011,13 +2007,13 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9">
         <v>127999</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2025,11 +2021,11 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" t="s">
-        <v>33</v>
+      <c r="F9">
+        <v>2222</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>33</v>
+        <v>255</v>
       </c>
       <c r="I9" s="5">
         <v>835</v>
@@ -2089,13 +2085,13 @@
         <v>34</v>
       </c>
       <c r="AB9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AC9" t="s">
         <v>57</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
@@ -2105,13 +2101,13 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10">
         <v>127999</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -2119,11 +2115,11 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="F10" t="s">
-        <v>33</v>
+      <c r="F10">
+        <v>1111</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>33</v>
+        <v>254</v>
       </c>
       <c r="I10" s="5">
         <v>799</v>
@@ -2183,13 +2179,13 @@
         <v>34</v>
       </c>
       <c r="AB10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AC10" t="s">
         <v>57</v>
       </c>
       <c r="AD10" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
@@ -2199,13 +2195,13 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11">
         <v>127999</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2213,11 +2209,11 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" t="s">
-        <v>33</v>
+      <c r="F11">
+        <v>2222</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>33</v>
+        <v>255</v>
       </c>
       <c r="I11" s="5">
         <v>738</v>
@@ -2277,13 +2273,13 @@
         <v>34</v>
       </c>
       <c r="AB11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC11" t="s">
         <v>57</v>
       </c>
       <c r="AD11" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
@@ -2293,13 +2289,13 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B12">
         <v>127999</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -2307,11 +2303,11 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" t="s">
-        <v>33</v>
+      <c r="F12">
+        <v>2222</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>33</v>
+        <v>255</v>
       </c>
       <c r="I12" s="5">
         <v>821</v>
@@ -2371,13 +2367,13 @@
         <v>34</v>
       </c>
       <c r="AB12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AC12" t="s">
         <v>57</v>
       </c>
       <c r="AD12" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
@@ -2387,13 +2383,13 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B13">
         <v>127999</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -2402,10 +2398,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I13" s="5">
         <v>813</v>
@@ -2465,13 +2461,13 @@
         <v>34</v>
       </c>
       <c r="AB13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC13" t="s">
         <v>57</v>
       </c>
       <c r="AD13" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
@@ -2481,28 +2477,28 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14">
         <v>127999</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" t="s">
         <v>88</v>
       </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="H14" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>252</v>
       </c>
       <c r="I14" s="5">
         <v>756</v>
@@ -2591,10 +2587,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I15" s="5">
         <v>858</v>
@@ -2685,10 +2681,10 @@
         <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I16" s="5">
         <v>1037</v>
@@ -2779,10 +2775,10 @@
         <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I17" s="5">
         <v>929</v>
@@ -2873,10 +2869,10 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I18" s="5">
         <v>772</v>
@@ -2972,8 +2968,8 @@
       <c r="G19" t="s">
         <v>111</v>
       </c>
-      <c r="H19" s="18" t="s">
-        <v>252</v>
+      <c r="H19" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="I19" s="5">
         <v>761</v>
@@ -3064,13 +3060,13 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G20" t="s">
         <v>117</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I20" s="5">
         <v>646</v>
@@ -3166,8 +3162,8 @@
       <c r="G21" t="s">
         <v>111</v>
       </c>
-      <c r="H21" s="18" t="s">
-        <v>252</v>
+      <c r="H21" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="I21" s="5">
         <v>487</v>
@@ -3258,10 +3254,10 @@
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I22" s="5">
         <v>572</v>
@@ -3352,10 +3348,10 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I23" s="5">
         <v>652</v>
@@ -3446,10 +3442,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I24" s="5">
         <v>584</v>
@@ -3540,10 +3536,10 @@
         <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I25" s="5">
         <v>645</v>
@@ -3634,10 +3630,10 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I26" s="5">
         <v>690</v>
@@ -3728,10 +3724,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I27" s="5">
         <v>638</v>
@@ -3822,10 +3818,10 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I28" s="5">
         <v>639</v>
@@ -3916,10 +3912,10 @@
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I29" s="5">
         <v>555</v>
@@ -4010,10 +4006,10 @@
         <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I30" s="5">
         <v>712</v>
@@ -4104,10 +4100,10 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I31" s="5">
         <v>712</v>
@@ -4198,10 +4194,10 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I32" s="5">
         <v>721</v>
@@ -4292,10 +4288,10 @@
         <v>0</v>
       </c>
       <c r="F33" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I33" s="5">
         <v>737</v>
@@ -4386,10 +4382,10 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I34" s="5">
         <v>574</v>
@@ -4480,13 +4476,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G35" t="s">
         <v>174</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I35" s="5">
         <v>903</v>
@@ -4575,13 +4571,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G36" t="s">
         <v>111</v>
       </c>
-      <c r="H36" s="18" t="s">
-        <v>252</v>
+      <c r="H36" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="I36" s="5">
         <v>514</v>
@@ -4672,10 +4668,10 @@
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I37" s="5">
         <v>524</v>
@@ -4766,10 +4762,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I38" s="5">
         <v>529</v>
@@ -4860,10 +4856,10 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I39" s="5">
         <v>538</v>
@@ -4954,10 +4950,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I40" s="5">
         <v>662</v>
@@ -5048,10 +5044,10 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I41" s="5">
         <v>878</v>
@@ -5142,10 +5138,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I42" s="5">
         <v>726</v>
@@ -5236,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I43" s="5">
         <v>1048</v>
@@ -5330,10 +5326,10 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I44" s="5">
         <v>811</v>
@@ -5424,10 +5420,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I45" s="5">
         <v>756</v>
@@ -5518,10 +5514,10 @@
         <v>2</v>
       </c>
       <c r="F46" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I46" s="5">
         <v>843</v>
@@ -5612,10 +5608,10 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I47" s="5">
         <v>821</v>
@@ -5706,10 +5702,10 @@
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I48" s="5">
         <v>967</v>
@@ -5800,10 +5796,10 @@
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I49" s="5">
         <v>695</v>
@@ -5894,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I50" s="5">
         <v>777</v>
@@ -5988,10 +5984,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I51" s="5">
         <v>417</v>
@@ -6087,8 +6083,8 @@
       <c r="G52" t="s">
         <v>111</v>
       </c>
-      <c r="H52" s="18" t="s">
-        <v>252</v>
+      <c r="H52" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="I52" s="5">
         <v>961</v>
@@ -6184,8 +6180,8 @@
       <c r="G53" t="s">
         <v>111</v>
       </c>
-      <c r="H53" s="18" t="s">
-        <v>252</v>
+      <c r="H53" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="I53" s="5">
         <v>917</v>
@@ -6276,13 +6272,13 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G54" t="s">
         <v>241</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I54" s="5">
         <v>502</v>
@@ -6373,13 +6369,13 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G55" t="s">
         <v>174</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I55" s="5">
         <v>530</v>
@@ -6459,54 +6455,54 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376870A8-036B-4D93-8027-6676A01067B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="8.7265625" style="18"/>
+    <col min="2" max="2" width="8.7265625" style="17" customWidth="1"/>
     <col min="3" max="3" width="27.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>255</v>
+      <c r="B4" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>249</v>
       </c>
       <c r="C5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
         <v>251</v>
-      </c>
-      <c r="C6" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" t="s">
         <v>252</v>
-      </c>
-      <c r="C7" t="s">
-        <v>253</v>
       </c>
     </row>
   </sheetData>
